--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1006.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1006.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day1 Opening+RT1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day2 RT2+TS+CS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen images" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Day1 Opening+RT1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Day2 RT2+TS+CS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Screen images" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B15"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="2" max="2"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林副大臣→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。</t>
+          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林室長→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。 1006b: 林氏の日本語肩書を「林室長」に統一（英語は Deputy Minister for Disaster Management のまま）。</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>・時間配分: 開会挨拶は Commissioner 5分・林 4〜5分・三浦 約4分（最後に開会宣言）・MC 計1〜2分（15分枠）。三浦原稿は draft1002_clean（児玉 rev4 受入、551語＝約4分）。
-・ADRC Opening 登壇順＝Commissioner → 林副大臣 → 三浦センター長（開会宣言）。アジェンダどおりの順で Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」により確定（9/30 の暫定順〈三浦→Commissioner→林〉は取り下げ）。RT はメンバー国 各5分まで（荒木田 9/29 決定、ベル方式）、アドバイザー国・ADPC・その他機関は4分（荒木田 10/1 決定。吉田は機関 5分を提案、登録者数次第で再調整）。TS は rev1.0（紹介5分＋発表15分×6枠＋質疑15分＋まとめ10分）。</t>
+・ADRC Opening 登壇順＝Commissioner → 林室長 → 三浦センター長（開会宣言）。アジェンダどおりの順で Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」により確定（9/30 の暫定順〈三浦→Commissioner→林〉は取り下げ）。RT はメンバー国 各5分まで（荒木田 9/29 決定、ベル方式）、アドバイザー国・ADPC・その他機関は4分（荒木田 10/1 決定。吉田は機関 5分を提案、登録者数次第で再調整）。TS は rev1.0（紹介5分＋発表15分×6枠＋質疑15分＋まとめ10分）。</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>未確定事項の確認先（内閣府分は 9/30 確定: 林副大臣は英語で挨拶、肩書 Deputy Minister for Disaster Management, Cabinet Office of Japan、Gala 欠席。内閣府スケジュール 9/28 版〈10/1 受領〉: 28 日 RT Part 1 の日本発言＝中根補佐、SC 議長＝中根補佐、林副大臣は 13:10 SIDEX 視察→15:30 MHA〈バイ会談・MoC 署名〉→22:20 発、御手洗参事官は 28 日 MHA 同行・Gala 代理出席・29 日 RT Part 2／TS／Closing／Field Trip 出席・22:50 発、中根補佐は 29 日 RT Part 2／TS／Closing／SCDF パレード、青木補佐・起塚は日本パビリオン担当で 30 日 22:20 発）。ADRC＝評価フォーム（用意・URL/QR）、RT の質問方式、Co-Moderator の要否。Sylvia（SCDF/COSEM）＝Commissioner の出席、Closing の SCDF 登壇者、フィールドトリップ集合場所、会場バナー前の写真。</t>
+          <t>未確定事項の確認先（内閣府分は 9/30 確定: 林室長は英語で挨拶、肩書 Deputy Minister for Disaster Management, Cabinet Office of Japan、Gala 欠席。内閣府スケジュール 9/28 版〈10/1 受領〉: 28 日 RT Part 1 の日本発言＝中根補佐、SC 議長＝中根補佐、林室長は 13:10 SIDEX 視察→15:30 MHA〈バイ会談・MoC 署名〉→22:20 発、御手洗参事官は 28 日 MHA 同行・Gala 代理出席・29 日 RT Part 2／TS／Closing／Field Trip 出席・22:50 発、中根補佐は 29 日 RT Part 2／TS／Closing／SCDF パレード、青木補佐・起塚は日本パビリオン担当で 30 日 22:20 発）。ADRC＝評価フォーム（用意・URL/QR）、RT の質問方式、Co-Moderator の要否。Sylvia（SCDF/COSEM）＝Commissioner の出席、Closing の SCDF 登壇者、フィールドトリップ集合場所、会場バナー前の写真。</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Sylvia 9/30 共有: 09:00-10:00 登録、10:00-10:05 オープニング映像、10:05-10:15 GOH Ms Sim Ann（Second Minister for Foreign Affairs / Home Affairs）、10:15-10:20 内閣府 林副大臣（5分、NFEC より先＝protocol 上位）、10:20-10:30 NFEC Chairman Mr Markham Shaw、10:30-11:15 FiSAC Keynote 1（Prof Guillermo Rein, Imperial College）、11:15-11:45 SCDF Sharing（SAC Ryan Ong）。ADRC 参加者の 10:30 以降の動線は協議中（FiSAC 出席は協定外、展示会見学を主張）。GOH 随行（ADRC 側、暫定 9/30）: 林副大臣＋通訳＋随行1、三浦センター長、北本理事。宮木所長は別グループだが Joint Opening では同席。</t>
+          <t>Sylvia 9/30 共有: 09:00-10:00 登録、10:00-10:05 オープニング映像、10:05-10:15 GOH Ms Sim Ann（Second Minister for Foreign Affairs / Home Affairs）、10:15-10:20 内閣府 林室長（5分、NFEC より先＝protocol 上位）、10:20-10:30 NFEC Chairman Mr Markham Shaw、10:30-11:15 FiSAC Keynote 1（Prof Guillermo Rein, Imperial College）、11:15-11:45 SCDF Sharing（SAC Ryan Ong）。ADRC 参加者の 10:30 以降の動線は協議中（FiSAC 出席は協定外、展示会見学を主張）。GOH 随行（ADRC 側、暫定 9/30）: 林室長＋通訳＋随行1、三浦センター長、北本理事。宮木所長は別グループだが Joint Opening では同席。</t>
         </is>
       </c>
       <c r="G6" s="6" t="n"/>
@@ -900,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 神戸（中村）が Sentio の共有を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に神戸が再開）。QR は共有開始後にしか発行されないため事前印刷は不可。共有開始直後に神戸から WhatsApp で届く QR 画像を藤本が PPT 08 に貼り、田中がポータブルプリンターで卓上の案内カードを印刷して 12:45 までに配る（間に合わなければ PPT 08 の掲示のみ）。参加者は各自の携帯や PC で言語を選ぶ。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林室長、三浦センター長）は12:40までに着席。12:40 神戸（中村）が Sentio の共有を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に神戸が再開）。QR は共有開始後にしか発行されないため事前印刷は不可。共有開始直後に神戸から WhatsApp で届く QR 画像を藤本が PPT 08 に貼り、田中がポータブルプリンターで卓上の案内カードを印刷して 12:45 までに配る（間に合わなければ PPT 08 の掲示のみ）。参加者は各自の携帯や PC で言語を選ぶ。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -988,7 +988,7 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>所要15分。挨拶 Commissioner 5分・林副大臣 4〜5分・三浦センター長 約4分（最後に開会宣言）＋MC 約1分。登壇順はアジェンダどおりで Sylvia 10/2 08:01 WhatsApp 確認済み（We are ok with the order!）。写真撮影は大使公邸レセプション（27日）で実施済み。会場バナー前の撮影は Sylvia が配置を検討中【TBC】。</t>
+          <t>所要15分。挨拶 Commissioner 5分・林室長 4〜5分・三浦センター長 約4分（最後に開会宣言）＋MC 約1分。登壇順はアジェンダどおりで Sylvia 10/2 08:01 WhatsApp 確認済み（We are ok with the order!）。写真撮影は大使公邸レセプション（27日）で実施済み。会場バナー前の撮影は Sylvia が配置を検討中【TBC】。</t>
         </is>
       </c>
       <c r="G10" s="6" t="n"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>日本語AI通訳は Zoom 内のみ（会場では案内しない）。Q&amp;A の方式は吉田・Gerry 回答待ち（10/3）。登壇順はアジェンダどおり Commissioner→林副大臣→三浦センター長（開会宣言）。Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」で確定。持ち時間: Commissioner 5分・林 4〜5分・三浦 約4分・MC 計1〜2分。</t>
+          <t>日本語AI通訳は Zoom 内のみ（会場では案内しない）。Q&amp;A の方式は吉田・Gerry 回答待ち（10/3）。登壇順はアジェンダどおり Commissioner→林室長→三浦センター長（開会宣言）。Sylvia 10/2 08:01 WhatsApp「We are ok with the order!」で確定。持ち時間: Commissioner 5分・林 4〜5分・三浦 約4分・MC 計1〜2分。</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>PPT 05: Name（林副大臣）</t>
+          <t>PPT 05: Name（林室長）</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>英語で挨拶（内閣府確認済、児玉 9/30）。通訳なし。肩書は Deputy Minister for Disaster Management, Cabinet Office of Japan（内閣府確認済）。挨拶後、林副大臣は Japan 席に着席、13:00 に退席（Japan 席は中根補佐に交代）。内閣府スケジュール（9/28 版）: 13:10 SIDEX 視察（御手洗参事官同行）→15:30 会場発→16:00 MHA でバイ会談・16:30 MoC 署名→22:20 発で帰国。Gala は欠席（児玉 9/30・10/1。9/28 スケジュールの 18:30-19:30 (P) は旧情報）、御手洗参事官が代理出席。</t>
+          <t>英語で挨拶（内閣府確認済、児玉 9/30）。通訳なし。肩書は Deputy Minister for Disaster Management, Cabinet Office of Japan（内閣府確認済）。挨拶後、林室長は Japan 席に着席、13:00 に退席（Japan 席は中根補佐に交代）。内閣府スケジュール（9/28 版）: 13:10 SIDEX 視察（御手洗参事官同行）→15:30 会場発→16:00 MHA でバイ会談・16:30 MoC 署名→22:20 発で帰国。Gala は欠席（児玉 9/30・10/1。9/28 スケジュールの 18:30-19:30 (P) は旧情報）、御手洗参事官が代理出席。</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>日本のステートメントは中根補佐（Mr NAKANE Toru, Director, International Relations Division, Disaster Management Bureau, Cabinet Office）。荒木田 10/1 確定、内閣府スケジュール 9/28 版と一致。林副大臣は Opening 後に退席、御手洗参事官は SIDEX 視察・MHA 同行で RT Part 1 不在。</t>
+          <t>日本のステートメントは中根補佐（Mr NAKANE Toru, Director, International Relations Division, Disaster Management Bureau, Cabinet Office）。荒木田 10/1 確定、内閣府スケジュール 9/28 版と一致。林室長は Opening 後に退席、御手洗参事官は SIDEX 視察・MHA 同行で RT Part 1 不在。</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5108,7 +5108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>氏名スライド（開会挨拶 3名: Commissioner → 林副大臣 → 三浦センター長）</t>
+          <t>氏名スライド（開会挨拶 3名: Commissioner → 林室長 → 三浦センター長）</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1006.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1006.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="B1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="2" max="2"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林室長→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。 1006b: 林氏の日本語肩書を「林室長」に統一（英語は Deputy Minister for Disaster Management のまま）。</t>
+          <t>作成: 2026-09-29 荒木田（ドラフト）。rev2 2026-09-30: 校閲版（0930_rev1_g）の赤字を反映（MC 文言の修正、RT 案内の箇条書き化、Co-Chair への確認依頼）。10/8（木）全体ブリーフィング（SCDF emcee・モデレーター、Google Meet）用。 rev3 2026-10-04: Opening の登壇順をアジェンダ順（Commissioner→林室長→三浦センター長が開会宣言）に確定（Sylvia 10/2 WhatsApp 確認）。PPT 03〜06 の割当、三浦原稿（draft1002_clean）の参照を更新。 同日: Azerbaijan の RT 発言辞退（10/1）を反映して Day1 の行を削除、以降の時刻と PPT 09 番号を繰り上げ。 10/5: 三浦センター長が開会・閉会挨拶案を了承（確定）。 10/6: Lao PDR の RT 発言辞退（10/5 吉田）で Day1 の行を削除、Pakistan 登録。 1006b: 林氏の日本語肩書を「林室長」に統一（英語は Deputy Minister for Disaster Management のまま）。 1006c: TS 発表 2 の JAXA を松尾氏に（池田 10/5）。</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="B1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>タイ・ウズベキスタンは参加未確定。未登録なら削除し、まとめを長く取る。</t>
+          <t>Thailand は登録済み（Part 1）。ウズベキスタンは未登録。未登録なら削除し、まとめを長く取る。</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Our second presentation is from JAXA. May I invite Japan Aerospace Exploration Agency (JAXA). Please.
+          <t>Our second presentation is from JAXA. May I invite Ms MATSUO Naoko, Director, Earth Observation Program Strategy Office, Japan Aerospace Exploration Agency (JAXA). Please.
 （発表 15分）
 Thank you very much.</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Japan Aerospace Exploration Agency (JAXA)【発表者 2名から選定中】</t>
+          <t>Ms MATSUO Naoko, Director, Earth Observation Program Strategy Office, JAXA（池田 10/5 確定。現地参加は松尾氏・上田氏）</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="B1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
